--- a/quizzes/019_exam_free_response_question_practice_form--quizzes.xlsx
+++ b/quizzes/019_exam_free_response_question_practice_form--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'lion'}</t>
+          <t>lion</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Lion'}</t>
+          <t>Lion</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'elephant'}</t>
+          <t>elephant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Elephant'}</t>
+          <t>Elephant</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cat'}</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cat'}</t>
+          <t>Cat</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pizza'}</t>
+          <t>pizza</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pizza'}</t>
+          <t>Pizza</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sushi'}</t>
+          <t>sushi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sushi'}</t>
+          <t>Sushi</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'rock'}</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Rock'}</t>
+          <t>Rock</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pop'}</t>
+          <t>pop</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Pop'}</t>
+          <t>Pop</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'classical'}</t>
+          <t>classical</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Classical'}</t>
+          <t>Classical</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'jazz'}</t>
+          <t>jazz</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Jazz'}</t>
+          <t>Jazz</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'hip-hop'}</t>
+          <t>hip-hop</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Hip-Hop'}</t>
+          <t>Hip-Hop</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'9-12th'}</t>
+          <t>9-12th</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '9-12th'}</t>
+          <t>9-12th</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'13-15th'}</t>
+          <t>13-15th</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '13-15th'}</t>
+          <t>13-15th</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'16-18th'}</t>
+          <t>16-18th</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '16-18th'}</t>
+          <t>16-18th</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'basketball'}</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Basketball'}</t>
+          <t>Basketball</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'soccer'}</t>
+          <t>soccer</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Soccer'}</t>
+          <t>Soccer</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'football'}</t>
+          <t>football</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Football'}</t>
+          <t>Football</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'math'}</t>
+          <t>math</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Math'}</t>
+          <t>Math</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'science'}</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Science'}</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'spring'}</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Spring'}</t>
+          <t>Spring</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'summer'}</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Summer'}</t>
+          <t>Summer</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fall'}</t>
+          <t>fall</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fall'}</t>
+          <t>Fall</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'winter'}</t>
+          <t>winter</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Winter'}</t>
+          <t>Winter</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
